--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_m_movinterna_a_2023_tarapaca.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_m_movinterna_a_2023_tarapaca.xlsx
@@ -138,7 +138,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 14:58</t>
+    <t xml:space="preserve">2026-09-24 01:47</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -570,19 +570,19 @@
         <v>8</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>-0.43</v>
+        <v>-0.23</v>
       </c>
       <c r="D2" s="2" t="n">
         <v>7</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>-0.66</v>
+        <v>-0.46</v>
       </c>
     </row>
     <row r="3">
@@ -593,19 +593,19 @@
         <v>8</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>-0.76</v>
+        <v>-0.56</v>
       </c>
       <c r="D3" s="2" t="n">
         <v>7</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>0.3</v>
+        <v>0.28</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>-1.05</v>
+        <v>-0.84</v>
       </c>
     </row>
     <row r="4">
@@ -616,19 +616,19 @@
         <v>8</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>-0.15</v>
+        <v>0.05</v>
       </c>
       <c r="D4" s="2" t="n">
         <v>7</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>0.23</v>
+        <v>0.18</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>-0.38</v>
+        <v>-0.13</v>
       </c>
     </row>
     <row r="5">
@@ -639,19 +639,19 @@
         <v>8</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>0.54</v>
+        <v>0.3</v>
       </c>
       <c r="D5" s="2" t="n">
         <v>7</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>-0.2</v>
+        <v>-0.11</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>0.74</v>
+        <v>0.41</v>
       </c>
     </row>
     <row r="6">
@@ -662,19 +662,19 @@
         <v>8</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>0.83</v>
+        <v>0.79</v>
       </c>
       <c r="D6" s="2" t="n">
         <v>7</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>-0.28</v>
+        <v>-0.27</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>1.12</v>
+        <v>1.05</v>
       </c>
     </row>
     <row r="7">
@@ -685,7 +685,7 @@
         <v>14</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>-0.92</v>
+        <v>-0.89</v>
       </c>
       <c r="D7" s="2" t="n">
         <v>7</v>
@@ -697,7 +697,7 @@
         <v>328</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>-0.66</v>
+        <v>-0.62</v>
       </c>
     </row>
     <row r="8">
@@ -708,19 +708,19 @@
         <v>14</v>
       </c>
       <c r="C8" s="2" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="D8" s="2" t="n">
         <v>7</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>0.03</v>
+        <v>0.09</v>
       </c>
       <c r="F8" s="2" t="n">
         <v>328</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>0.47</v>
+        <v>0.61</v>
       </c>
     </row>
     <row r="9">
@@ -731,19 +731,19 @@
         <v>14</v>
       </c>
       <c r="C9" s="2" t="n">
-        <v>0.26</v>
+        <v>0.47</v>
       </c>
       <c r="D9" s="2" t="n">
         <v>7</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>-0.01</v>
+        <v>0.03</v>
       </c>
       <c r="F9" s="2" t="n">
         <v>328</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>0.27</v>
+        <v>0.44</v>
       </c>
     </row>
     <row r="10">
@@ -754,19 +754,19 @@
         <v>14</v>
       </c>
       <c r="C10" s="2" t="n">
-        <v>-0.73</v>
+        <v>-0.75</v>
       </c>
       <c r="D10" s="2" t="n">
         <v>7</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>-0.24</v>
+        <v>-0.16</v>
       </c>
       <c r="F10" s="2" t="n">
         <v>328</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>-0.49</v>
+        <v>-0.59</v>
       </c>
     </row>
     <row r="11">
@@ -777,19 +777,19 @@
         <v>14</v>
       </c>
       <c r="C11" s="2" t="n">
-        <v>-0.74</v>
+        <v>-0.75</v>
       </c>
       <c r="D11" s="2" t="n">
         <v>7</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>-0.23</v>
+        <v>-0.15</v>
       </c>
       <c r="F11" s="2" t="n">
         <v>328</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>-0.51</v>
+        <v>-0.6</v>
       </c>
     </row>
     <row r="12">
@@ -800,19 +800,19 @@
         <v>14</v>
       </c>
       <c r="C12" s="2" t="n">
-        <v>-0.69</v>
+        <v>-0.85</v>
       </c>
       <c r="D12" s="2" t="n">
         <v>7</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>-0.48</v>
+        <v>-0.42</v>
       </c>
       <c r="F12" s="2" t="n">
         <v>328</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>-0.21</v>
+        <v>-0.43</v>
       </c>
     </row>
     <row r="13">
@@ -823,19 +823,19 @@
         <v>14</v>
       </c>
       <c r="C13" s="2" t="n">
-        <v>-0.67</v>
+        <v>-0.83</v>
       </c>
       <c r="D13" s="2" t="n">
         <v>7</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>-0.43</v>
+        <v>-0.38</v>
       </c>
       <c r="F13" s="2" t="n">
         <v>328</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>-0.24</v>
+        <v>-0.45</v>
       </c>
     </row>
     <row r="14">
@@ -846,19 +846,19 @@
         <v>14</v>
       </c>
       <c r="C14" s="2" t="n">
-        <v>0.5</v>
+        <v>0.56</v>
       </c>
       <c r="D14" s="2" t="n">
         <v>7</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>-0.32</v>
+        <v>-0.22</v>
       </c>
       <c r="F14" s="2" t="n">
         <v>328</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>0.82</v>
+        <v>0.78</v>
       </c>
     </row>
     <row r="15">
@@ -869,19 +869,19 @@
         <v>14</v>
       </c>
       <c r="C15" s="2" t="n">
-        <v>-0.1</v>
+        <v>0.16</v>
       </c>
       <c r="D15" s="2" t="n">
         <v>7</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>-0.22</v>
+        <v>-0.15</v>
       </c>
       <c r="F15" s="2" t="n">
         <v>328</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>0.12</v>
+        <v>0.32</v>
       </c>
     </row>
     <row r="16">
@@ -892,19 +892,19 @@
         <v>14</v>
       </c>
       <c r="C16" s="2" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="D16" s="2" t="n">
         <v>7</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>0.15</v>
+        <v>0.11</v>
       </c>
       <c r="F16" s="2" t="n">
         <v>328</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>0.26</v>
+        <v>0.39</v>
       </c>
     </row>
     <row r="17">
@@ -915,19 +915,19 @@
         <v>14</v>
       </c>
       <c r="C17" s="2" t="n">
-        <v>-0.38</v>
+        <v>-0.24</v>
       </c>
       <c r="D17" s="2" t="n">
         <v>7</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>0.23</v>
+        <v>0.14</v>
       </c>
       <c r="F17" s="2" t="n">
         <v>328</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>-0.6</v>
+        <v>-0.38</v>
       </c>
     </row>
     <row r="18">
@@ -938,19 +938,19 @@
         <v>26</v>
       </c>
       <c r="C18" s="2" t="n">
-        <v>-0.77</v>
+        <v>-0.58</v>
       </c>
       <c r="D18" s="2" t="n">
         <v>7</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>0.31</v>
+        <v>0.28</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>-1.09</v>
+        <v>-0.86</v>
       </c>
     </row>
     <row r="19">
@@ -961,19 +961,19 @@
         <v>28</v>
       </c>
       <c r="C19" s="2" t="n">
-        <v>-0.66</v>
+        <v>-0.51</v>
       </c>
       <c r="D19" s="2" t="n">
         <v>7</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>-0.04</v>
+        <v>-0.16</v>
       </c>
       <c r="F19" s="2" t="n">
         <v>328</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>-0.62</v>
+        <v>-0.35</v>
       </c>
     </row>
     <row r="20">
@@ -984,19 +984,19 @@
         <v>28</v>
       </c>
       <c r="C20" s="2" t="n">
-        <v>-0.55</v>
+        <v>-0.42</v>
       </c>
       <c r="D20" s="2" t="n">
         <v>7</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>0.21</v>
+        <v>0.11</v>
       </c>
       <c r="F20" s="2" t="n">
         <v>328</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>-0.76</v>
+        <v>-0.53</v>
       </c>
     </row>
     <row r="21">
@@ -1007,19 +1007,19 @@
         <v>31</v>
       </c>
       <c r="C21" s="2" t="n">
-        <v>-0.05</v>
+        <v>-0.31</v>
       </c>
       <c r="D21" s="2" t="n">
         <v>7</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>-0.25</v>
+        <v>-0.37</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>0.2</v>
+        <v>0.06</v>
       </c>
     </row>
     <row r="22">
@@ -1030,16 +1030,16 @@
         <v>31</v>
       </c>
       <c r="C22" s="2" t="n">
-        <v>-0.22</v>
+        <v>-0.47</v>
       </c>
       <c r="D22" s="2" t="n">
         <v>7</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>-0.11</v>
+        <v>-0.36</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="G22" s="2" t="n">
         <v>-0.11</v>
@@ -1053,7 +1053,7 @@
         <v>31</v>
       </c>
       <c r="C23" s="2" t="n">
-        <v>0.15</v>
+        <v>-0.05</v>
       </c>
       <c r="D23" s="2" t="n">
         <v>7</v>
@@ -1062,10 +1062,10 @@
         <v>-0.22</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="G23" s="2" t="n">
-        <v>0.36</v>
+        <v>0.17</v>
       </c>
     </row>
     <row r="24">
@@ -1076,19 +1076,19 @@
         <v>31</v>
       </c>
       <c r="C24" s="2" t="n">
-        <v>0.49</v>
+        <v>0.54</v>
       </c>
       <c r="D24" s="2" t="n">
         <v>7</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>-0.05</v>
+        <v>0.01</v>
       </c>
       <c r="F24" s="2" t="n">
         <v>345</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>0.54</v>
+        <v>0.53</v>
       </c>
     </row>
     <row r="25">
@@ -1099,7 +1099,7 @@
         <v>31</v>
       </c>
       <c r="C25" s="2" t="n">
-        <v>-0.22</v>
+        <v>-0.05</v>
       </c>
       <c r="D25" s="2" t="n">
         <v>7</v>
@@ -1108,10 +1108,10 @@
         <v>0.35</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="G25" s="2" t="n">
-        <v>-0.57</v>
+        <v>-0.4</v>
       </c>
     </row>
     <row r="26">
@@ -1122,19 +1122,19 @@
         <v>31</v>
       </c>
       <c r="C26" s="2" t="n">
-        <v>-0.65</v>
+        <v>-0.5</v>
       </c>
       <c r="D26" s="2" t="n">
         <v>7</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>-0.08</v>
+        <v>-0.14</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>-0.57</v>
+        <v>-0.36</v>
       </c>
     </row>
   </sheetData>

--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_m_movinterna_a_2023_tarapaca.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_m_movinterna_a_2023_tarapaca.xlsx
@@ -138,7 +138,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-24 01:47</t>
+    <t xml:space="preserve">2026-10-01 23:22</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -153,7 +153,7 @@
     <t xml:space="preserve">plot_regional_correl_matriz_m_movinterna_a_2023_tarapaca.png</t>
   </si>
   <si>
-    <t xml:space="preserve">Movilidad interna (CMI)</t>
+    <t xml:space="preserve">Movilidad interna comunal (CMI)</t>
   </si>
   <si>
     <t xml:space="preserve">Unidad territorial</t>

--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_m_movinterna_a_2023_tarapaca.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_m_movinterna_a_2023_tarapaca.xlsx
@@ -138,7 +138,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-01 23:22</t>
+    <t xml:space="preserve">2026-10-05 20:06</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
